--- a/blocks_pilot.xlsx
+++ b/blocks_pilot.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Backups\All Files\Genel\Is\2022\Upwork\LabX\studies\materials\drivingSimulator\repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346BAA67-4042-43CD-AC18-98E4C49AF247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8010566B-C909-4ACB-AFB0-5CADBCF99A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25875" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>current_font</t>
   </si>
@@ -112,6 +112,15 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>scoreRegistry</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>lexical_only</t>
   </si>
 </sst>
 </file>
@@ -429,14 +438,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +479,11 @@
       <c r="K1" t="s">
         <v>24</v>
       </c>
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -505,8 +517,11 @@
       <c r="K2" t="s">
         <v>9</v>
       </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -540,8 +555,11 @@
       <c r="K3" t="s">
         <v>9</v>
       </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -575,8 +593,11 @@
       <c r="K4" t="s">
         <v>9</v>
       </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -610,8 +631,11 @@
       <c r="K5" t="s">
         <v>25</v>
       </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -645,8 +669,11 @@
       <c r="K6" t="s">
         <v>25</v>
       </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -679,6 +706,9 @@
       </c>
       <c r="K7" t="s">
         <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
